--- a/per-stock/NVDA/financials.xlsx
+++ b/per-stock/NVDA/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5457368842240</v>
+        <v>5103122644992</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5424132128768</v>
+        <v>5058340061184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46.077713</v>
+        <v>32.26493</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.820166</v>
+        <v>16.551956</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25.27285</v>
+        <v>20.131376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.71068</v>
+        <v>0.74144995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -621,7 +630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.65024</v>
+        <v>0.65596</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -636,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.55603004</v>
+        <v>0.62966</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,7 +660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.01485</v>
+        <v>1.14288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -666,7 +675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.732</v>
+        <v>0.852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -681,7 +690,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62556000256</v>
+        <v>53171998720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11411999744</v>
+        <v>12814000128</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58128998400</v>
+        <v>119076000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24220525225</v>
+        <v>24221000000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>225.32</v>
+        <v>210.69</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B39:E39)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D41</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C41</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B41</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B37:E37)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D37</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C37</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B37</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B33:E33)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B8:E8)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B5:E5)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1698,7 +2178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1723,27 +2203,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
         </is>
       </c>
     </row>
@@ -1776,19 +2256,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.165687</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.147585</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.158846</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.153</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0.143</v>
-      </c>
       <c r="F3" s="3" t="n">
-        <v>0.123964</v>
+        <v>0.143085</v>
       </c>
     </row>
     <row r="4">
@@ -1798,19 +2278,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>71002000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>51283000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>38748000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>31937000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>22584000000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>25821000000</v>
       </c>
     </row>
     <row r="5">
@@ -1820,19 +2300,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>58321000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>42960000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>31910000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>26422000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>18775000000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>22091000000</v>
       </c>
     </row>
     <row r="6">
@@ -1842,19 +2322,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>997000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>812000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>751000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>669000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>611000000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>543000000</v>
       </c>
     </row>
     <row r="7">
@@ -1864,19 +2344,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>20458000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>17034000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>15157000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>12890000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>17394000000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>10608000000</v>
       </c>
     </row>
     <row r="8">
@@ -1886,19 +2366,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>71002000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>51283000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>38748000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>31937000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>22584000000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>25821000000</v>
       </c>
     </row>
     <row r="9">
@@ -1908,19 +2388,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>70005000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>50471000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>37997000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>31268000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>21973000000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>25278000000</v>
       </c>
     </row>
     <row r="10">
@@ -1930,19 +2410,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>438000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>495000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>563000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>530000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>452000000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>450000000</v>
       </c>
     </row>
     <row r="11">
@@ -1952,19 +2432,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>73000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>61000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>63000000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>61000000</v>
       </c>
     </row>
     <row r="12">
@@ -1974,19 +2454,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>540000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>568000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>624000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>592000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>515000000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>511000000</v>
       </c>
     </row>
     <row r="13">
@@ -1996,19 +2476,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>58321000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>42960000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>31910000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>26422000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>18775000000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>22091000000</v>
       </c>
     </row>
     <row r="14">
@@ -2018,19 +2498,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>58321000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>42960000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>31910000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>26422000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>18775000000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>22091000000</v>
       </c>
     </row>
     <row r="15">
@@ -2040,19 +2520,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>28079000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>23828000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>20996000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>18303000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>22424000000</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>15297000000</v>
       </c>
     </row>
     <row r="16">
@@ -2062,19 +2542,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>53536000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>44299000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>36010000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>28440000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>21638000000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>24034000000</v>
       </c>
     </row>
     <row r="17">
@@ -2084,19 +2564,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>24391000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>24432000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>24483000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>24532000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>24611000000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>24706000000</v>
       </c>
     </row>
     <row r="18">
@@ -2106,19 +2586,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>24286000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>24304000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>24327000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>24366000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>24441000000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>24489000000</v>
       </c>
     </row>
     <row r="19">
@@ -2128,19 +2608,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>1.76</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>0.76</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0.89</v>
       </c>
     </row>
     <row r="20">
@@ -2150,19 +2630,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>1.77</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>1.08</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>0.77</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -2172,19 +2652,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>58321000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>42960000000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>31910000000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>26422000000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>18775000000</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>22091000000</v>
       </c>
     </row>
     <row r="22">
@@ -2194,19 +2674,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>58321000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>42960000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>31910000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>26422000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>18775000000</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>22091000000</v>
       </c>
     </row>
     <row r="23">
@@ -2216,19 +2696,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>58321000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>42960000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>31910000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>26422000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>18775000000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>22091000000</v>
       </c>
     </row>
     <row r="24">
@@ -2238,19 +2718,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>58321000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>42960000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>31910000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>26422000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>18775000000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>22091000000</v>
       </c>
     </row>
     <row r="25">
@@ -2260,19 +2740,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>58321000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>42960000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>31910000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>26422000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>18775000000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>22091000000</v>
       </c>
     </row>
     <row r="26">
@@ -2282,19 +2762,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>11582000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>7438000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>6026000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>4784000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>3135000000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>3126000000</v>
       </c>
     </row>
     <row r="27">
@@ -2304,19 +2784,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>69903000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>50398000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>37936000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>31206000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>21910000000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>25217000000</v>
       </c>
     </row>
     <row r="28">
@@ -2326,19 +2806,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>15929000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>5604000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>1363000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>2236000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-180000000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>733000000</v>
       </c>
     </row>
     <row r="29">
@@ -2348,19 +2828,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>15929000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>5604000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>1363000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>2236000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-180000000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>733000000</v>
       </c>
     </row>
     <row r="30">
@@ -2370,19 +2850,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>438000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>495000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>563000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>530000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>452000000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>450000000</v>
       </c>
     </row>
     <row r="31">
@@ -2392,19 +2872,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>73000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>61000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>63000000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>61000000</v>
       </c>
     </row>
     <row r="32">
@@ -2414,19 +2894,19 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>540000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>568000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>624000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>592000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>515000000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>511000000</v>
       </c>
     </row>
     <row r="33">
@@ -2436,19 +2916,19 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>53536000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>44299000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>36010000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>28440000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>21638000000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>24034000000</v>
       </c>
     </row>
     <row r="34">
@@ -2458,19 +2938,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>7621000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>6794000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>5839000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>5413000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>5030000000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>4689000000</v>
       </c>
     </row>
     <row r="35">
@@ -2480,19 +2960,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>6321000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>5512000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>4705000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>4291000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>3989000000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>3714000000</v>
       </c>
     </row>
     <row r="36">
@@ -2502,19 +2982,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>1282000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>1134000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>1122000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>1041000000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>975000000</v>
       </c>
     </row>
     <row r="37">
@@ -2524,19 +3004,19 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>61157000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>51093000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>41849000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>33853000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>26668000000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>28723000000</v>
       </c>
     </row>
     <row r="38">
@@ -2546,19 +3026,19 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>20458000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>17034000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>15157000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>12890000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>17394000000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>10608000000</v>
       </c>
     </row>
     <row r="39">
@@ -2568,19 +3048,19 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>81615000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>68127000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>57006000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>46743000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>44062000000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>39331000000</v>
       </c>
     </row>
     <row r="40">
@@ -2590,19 +3070,19 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>81615000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>68127000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>57006000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>46743000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>44062000000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>39331000000</v>
       </c>
     </row>
   </sheetData>
@@ -2610,7 +3090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4234,7 +4714,1883 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>24220525225</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>24304000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>24305000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>24347000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>24387557065</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>24220525225</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>24304000000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>24305000000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>24347000000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>24387557065</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>12348000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>11040000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>10481000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>10598000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>10285000000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>171460000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>133155000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>111700000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>93621000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>77576000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>203944000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>165761000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>127364000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>108597000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>92307000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>107111000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>93442000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>90417000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>77962000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>63393000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>171460000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>133155000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>111700000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>93621000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>77576000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>3878000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2572000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2014000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2132000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1821000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>195474000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>157293000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>118897000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>100131000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>83843000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>202944000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>164762000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>126365000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>108597000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>92307000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>195474000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>157293000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>118897000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>100131000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>83843000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>195474000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>157293000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>118897000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>100131000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>83843000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>137000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>178000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>339000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>170000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>186000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>137000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>178000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>339000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>170000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>186000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>185038000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>146973000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>107908000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>88737000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>72158000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>10275000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>10118000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>10626000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>11200000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>11475000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>64000000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>49510000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>42251000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>40609000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>41411000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>20116000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>17347000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>16176000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>16352000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>14869000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>737000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>381000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>376000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>243000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>177000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>4830000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>3958000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>3532000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>3406000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2621000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>3201000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2967000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2786000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2406000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2086000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1403000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1193000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1165000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1055000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1004000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1798000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1774000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1621000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1351000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1082000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>11348000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>10041000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>9482000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>10297000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>9985000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>3878000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2572000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>2014000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1831000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1521000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>7470000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>7469000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>7468000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>8466000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>8464000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>43884000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>32163000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>26075000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>24257000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>26542000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>2194000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1373000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1196000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>202000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>228000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1714000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1379000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1248000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>980000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1074000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1714000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1379000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1248000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>980000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1074000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>999000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>999000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>301000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n">
+        <v>301000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>288000000</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>273000000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>999000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>999000000</v>
+      </c>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>999000000</v>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Provisions</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2948000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2807000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>2707000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2245000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2168000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>36028000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>25605000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>19925000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>20529000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>22772000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>12293000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>13124000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>8386000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>9555000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>9769000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>23735000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>12481000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>11539000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>10974000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>13003000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>10638000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>2669000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>2915000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1910000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>5672000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>13097000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>9812000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>8624000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>9064000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>7331000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>259474000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>206803000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>161148000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>140740000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>125254000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>108479000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>81198000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>44656000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>38521000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>35319000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>12733000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>8301000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>632000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>272000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Non Current Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n">
+        <v>1536000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2103000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2413000000</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>2087000000</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>2387000000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>11707000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>13258000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>13674000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>13570000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>13318000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>11707000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>13258000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>13674000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>13570000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>13318000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Non Current Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n"/>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n">
+        <v>1369000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1042000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>895000000</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>750000000</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>568000000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>43364000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>22251000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>8187000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>3799000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>3240000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n">
+        <v>2237000000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>43364000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>22251000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>8187000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>3799000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>3240000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>43364000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>22251000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>8187000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>3799000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>3240000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>24014000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>24138000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>7197000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>6510000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>6267000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>3120000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>3306000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>936000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>755000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>769000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>20894000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>20832000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>6261000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>5755000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>5498000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>16661000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>13250000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>12061000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>11225000000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>8946000000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n">
+        <v>-6587000000</v>
+      </c>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>-4401000000</v>
+      </c>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>16661000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>19837000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>12061000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>11225000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>8946000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n">
+        <v>683000000</v>
+      </c>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n">
+        <v>529000000</v>
+      </c>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>16661000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>2867000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>12061000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>11225000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>8946000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n">
+        <v>12619000000</v>
+      </c>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n"/>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n">
+        <v>7568000000</v>
+      </c>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n">
+        <v>2891000000</v>
+      </c>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n">
+        <v>2076000000</v>
+      </c>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n">
+        <v>777000000</v>
+      </c>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n">
+        <v>511000000</v>
+      </c>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n"/>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>150995000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>125605000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>116492000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>102219000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>89935000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>3916000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>3180000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>2709000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2658000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2779000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n">
+        <v>2800000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>25797000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>21403000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>19784000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>14962000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>11333000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>9201000000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>8774000000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>6840000000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>8708000000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>3469000000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>9949000000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>8822000000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>8735000000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>4411000000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>5339000000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>6647000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>3807000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>4209000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1843000000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>2525000000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>40710000000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>38466000000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>33391000000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>27808000000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>22132000000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>40710000000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>38466000000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>33391000000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>27808000000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>22132000000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>80572000000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>62556000000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>60608000000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>53991000000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>52691000000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>67335000000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>51951000000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>49122000000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>42352000000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>37457000000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>13237000000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>10605000000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>11486000000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>11639000000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>15234000000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5394,13 +7750,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5410,6 +7766,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5420,30 +7777,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5456,21 +7818,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>48587000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>34904000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>22115000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>13470000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>26187000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>15552000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5479,21 +7842,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-19312000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-3815000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-12456000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-9720000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-14095000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-7811000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5501,20 +7865,21 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5523,21 +7888,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-1757000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-1284000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-1636000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>-1895000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-1227000000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-1077000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5545,18 +7911,19 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n">
         <v>6979000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>4858000000</v>
       </c>
-      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n">
         <v>4129000000</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>3540000000</v>
       </c>
     </row>
@@ -5567,21 +7934,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>13237000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>10605000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>11486000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>11639000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>15234000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>8589000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5590,21 +7958,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>10605000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>11486000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>11639000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>15234000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>8589000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>9107000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5613,21 +7982,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>2632000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>-881000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>-153000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>-3595000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>6645000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>-518000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5636,21 +8006,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-21283000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-6208000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-14880000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-11833000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-15553000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-9949000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5659,21 +8030,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-21283000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-6208000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-14880000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-11833000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-15553000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-9949000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5682,21 +8054,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-2243000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-2152000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-2453000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-1869000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-1584000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-1894000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5705,21 +8078,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>515000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>273000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>370000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>1000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5728,10 +8102,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-243000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-242000000</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>-244000000</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>-244000000</v>
@@ -5740,9 +8114,10 @@
         <v>-244000000</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-245000000</v>
+        <v>-244000000</v>
       </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5751,10 +8126,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-243000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-242000000</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>-244000000</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>-244000000</v>
@@ -5763,9 +8138,10 @@
         <v>-244000000</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-245000000</v>
+        <v>-244000000</v>
       </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5774,21 +8150,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-19312000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-3815000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-12456000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-9720000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-14095000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-7811000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5797,21 +8174,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-19312000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-3815000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-12456000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-9720000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-14095000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-7811000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5819,20 +8197,21 @@
           <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H18" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5840,20 +8219,21 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H19" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5861,20 +8241,21 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B20" s="3" t="n"/>
       <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H20" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5883,21 +8264,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-26429000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>-30861000000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-9024000000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>-7127000000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-5216000000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-7198000000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5906,21 +8288,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-26429000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-30861000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-9024000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-7127000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-5216000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-7198000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5929,21 +8312,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-24585000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-16412000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-6695000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-4938000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-3606000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-5601000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5952,21 +8336,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>1997000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>16928000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>2730000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>3220000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>3589000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>1887000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5975,21 +8360,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-26582000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-33340000000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-9425000000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-8158000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-7195000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-7488000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5998,21 +8384,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-87000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-13165000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-693000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-294000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-383000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-542000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6025,7 +8412,8 @@
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n">
         <v>66000000</v>
       </c>
     </row>
@@ -6036,21 +8424,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-87000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-13165000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-693000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-294000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-383000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-542000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6059,21 +8448,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-1757000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-1284000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-1636000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-1895000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-1227000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-1077000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6082,21 +8472,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-1757000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-1284000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-1636000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-1895000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-1227000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-1077000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6105,21 +8496,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>50344000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>36188000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>23751000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>15365000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>27414000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>16629000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6128,21 +8520,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>50344000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>36188000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>23751000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>15365000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>27414000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>16629000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6151,21 +8544,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>3544000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-4325000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-9256000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-11022000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>8654000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-5863000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6174,21 +8568,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>1217000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>533000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>332000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>629000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>350000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>372000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6197,21 +8592,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>9973000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>2117000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>906000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-2739000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>8069000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>1227000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6220,21 +8616,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>7763000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>1053000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>1129000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-4053000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>7128000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>360000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6243,21 +8640,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>2210000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>1064000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-223000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>1314000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>941000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>867000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6266,21 +8664,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>2210000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1064000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-223000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>1314000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>941000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>867000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6289,21 +8688,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-983000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-280000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-89000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>386000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>560000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>331000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6312,21 +8712,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-4420000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-1621000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-4823000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-3622000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-1258000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-2424000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6335,21 +8736,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-2243000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-5074000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-5582000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-5676000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>933000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-5369000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6358,21 +8760,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-2243000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-5074000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-5582000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-5676000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>933000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-5369000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6381,21 +8784,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-94000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-80000000</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>-98000000</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>-98000000</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>-137000000</v>
+        <v>-98000000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6404,21 +8808,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>1928000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>1633000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>1654000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>1625000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>1474000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>1321000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6427,21 +8832,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>1584000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>611000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>125000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>17000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>-2177000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-598000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6450,21 +8856,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>1584000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>611000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>125000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>17000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-2177000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-598000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6473,21 +8880,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>997000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>812000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>751000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>669000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>611000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>543000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6496,21 +8904,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>997000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>812000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>751000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>669000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>611000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>543000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6519,21 +8928,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-15936000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>-5492000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>-1353000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>-2248000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>-728000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6542,21 +8952,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>-15936000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>-5492000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>-1353000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>-2248000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>175000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>-728000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6569,7 +8980,8 @@
       <c r="D51" s="3" t="n"/>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n">
         <v>-38000000</v>
       </c>
     </row>
@@ -6580,28 +8992,29 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>58321000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>42960000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>31910000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>26422000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>18775000000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>22091000000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
